--- a/backtest_runs/20260410_193731/by_symbol/INIL/INIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/INIL/INIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-4467.520000000016</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>95532.47999999998</v>
@@ -633,7 +633,7 @@
         <v>-8228.480000000005</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>93088.95999999999</v>
@@ -679,7 +679,7 @@
         <v>-10304</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>82784.95999999999</v>
@@ -909,7 +909,7 @@
         <v>-5365.439999999994</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>86597.44</v>
@@ -1047,7 +1047,7 @@
         <v>-772.8000000000084</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>89048.31999999998</v>
@@ -1231,7 +1231,7 @@
         <v>-1781.120000000012</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>96040.31999999998</v>
@@ -1277,7 +1277,7 @@
         <v>-5880.639999999986</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>90159.67999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-1604.480000000005</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>95046.71999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-1472</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>93574.71999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-1324.800000000008</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>94156.15999999997</v>
